--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -843,7 +843,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.123.xlsx
@@ -422,17 +422,17 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
-    <col width="27" customWidth="1" min="10" max="10"/>
+    <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="42" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
@@ -607,14 +607,22 @@
           <t>L17: punctuation artifact: repeated periods | line starts with digit/letter garbage token | suspicious token(s): 5Aug (letter/digit mix) :: 5Aug., 1818....</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr"/>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
+        </is>
+      </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L49: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ to</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]116 MISCELLANEOUS ORDERS.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]116 MISCELLANEOUS ORDERS.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L9: isolated marker/symbol line :: a</t>
@@ -661,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>51</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -677,7 +685,7 @@
       <c r="J3" s="1" t="inlineStr"/>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -697,7 +705,7 @@
       <c r="R3" s="1" t="inlineStr"/>
       <c r="S3" s="1" t="inlineStr">
         <is>
-          <t>L63: line starts with digit/letter garbage token | suspicious token(s): 9Payment (letter/digit mix) :: 9Payment by proceed by reason of the Solicitor for any party having</t>
+          <t>L49: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • to</t>
         </is>
       </c>
       <c r="T3" s="1" t="inlineStr"/>
@@ -730,7 +738,11 @@
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr"/>
-      <c r="K4" s="1" t="inlineStr"/>
+      <c r="K4" s="1" t="inlineStr">
+        <is>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
+        </is>
+      </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
@@ -740,13 +752,17 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L55: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr"/>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L63: line starts with digit/letter garbage token | suspicious token(s): 9Payment (letter/digit mix) :: 9Payment by proceed by reason of the Solicitor for any party having</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -767,7 +783,7 @@
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -825,7 +841,7 @@
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L104: isolated marker/symbol line :: æ°”</t>
+          <t>L104: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr"/>
@@ -969,12 +985,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1013,7 +1029,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1130,7 +1146,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
